--- a/tests/regression_artifacts/downloads/email_03152025_0.00/current/HAWB9573874.xlsx
+++ b/tests/regression_artifacts/downloads/email_03152025_0.00/current/HAWB9573874.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,11 +52,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="10"/>
     </font>
@@ -74,7 +69,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -91,12 +86,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEBCC"/>
-        <bgColor rgb="00FFEBCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -130,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -145,21 +134,19 @@
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK53"/>
+  <dimension ref="A1:AK51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -766,27 +753,31 @@
           <t>114-5494833-4517814</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Unclassifiable / Non-physical goods</t>
+          <t>ALUMINUM ARTICLES</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>99999999</t>
+          <t>76169990</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>99999999</t>
+          <t>76169990</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Aug 24, 9:34 AM ~ Morne Fendue St. Patrick, St. Patrick Grenada Amazon.com - Order 114-5494833-4517814 Estimated tax to be collected: (1 items)</t>
+          <t>Thinp 8 Pcs Mic Stand Adapter,Aluminum Alloy Microphone Stand Screw Stand Ada... (1 items)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -800,10 +791,10 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="Q2" s="3">
         <f>O2*K2</f>
@@ -814,7 +805,7 @@
         <v/>
       </c>
       <c r="S2" s="3" t="n">
-        <v>3</v>
+        <v>39.59</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>3</v>
@@ -834,22 +825,22 @@
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>TEMU</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>TEMU</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>31 St. James Avenue, Suite 355, Boston, MA 02116</t>
+          <t>410 Terry Avenue North, Seattle, WA 98109</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AD2" s="2" t="n"/>
@@ -861,7 +852,7 @@
       <c r="AJ2" s="2" t="n"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>99999999</t>
+          <t>76169990</t>
         </is>
       </c>
     </row>
@@ -873,19 +864,19 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>99999999</t>
+          <t>76169990</t>
         </is>
       </c>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>TEMU-1</t>
+          <t>AMZ-1</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Aug 24, 9:34 AM ~ Morne Fendue St. Patrick, St. Patrick Grenada Amazon.com - Order 114-5494833-4517814 Estimated tax to be collected:</t>
+          <t>Thinp 8 Pcs Mic Stand Adapter,Aluminum Alloy Microphone Stand Screw Stand Ada...</t>
         </is>
       </c>
       <c r="K3" s="4" t="n">
@@ -899,10 +890,10 @@
         </is>
       </c>
       <c r="O3" s="5" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="Q3" s="5">
         <f>O3*K3</f>
@@ -940,27 +931,31 @@
           <t>114-5494833-4517814</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Unclassifiable / Non-physical goods</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>00000000</t>
+          <t>64031900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>00000000</t>
+          <t>64031900</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Grand Total: (1 items)</t>
+          <t>Element Men's Topaz C3 Skate Shoe, Grey, 12 (1 items)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -974,10 +969,10 @@
         </is>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q4" s="3">
         <f>O4*K4</f>
@@ -1007,7 +1002,7 @@
       <c r="AJ4" s="2" t="n"/>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>00000000</t>
+          <t>64031900</t>
         </is>
       </c>
     </row>
@@ -1019,19 +1014,19 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>00000000</t>
+          <t>64031900</t>
         </is>
       </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>TEMU-3</t>
+          <t>AMZ-3</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Grand Total:</t>
+          <t>Element Men's Topaz C3 Skate Shoe, Grey, 12</t>
         </is>
       </c>
       <c r="K5" s="4" t="n">
@@ -1045,10 +1040,10 @@
         </is>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="5">
         <f>O5*K5</f>
@@ -1612,9 +1607,9 @@
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
-      <c r="J21" s="13" t="inlineStr">
-        <is>
-          <t>INVOICE NOTES: Invoice total uncertain</t>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>DUTY ESTIMATION (Classification Cross-Check)</t>
         </is>
       </c>
       <c r="K21" s="12" t="n"/>
@@ -1645,456 +1640,516 @@
       <c r="AJ21" s="12" t="n"/>
       <c r="AK21" s="12" t="n"/>
     </row>
-    <row r="22"/>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="13" t="n"/>
+      <c r="I22" s="13" t="n"/>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>CIF (USD) = InvTotal + Freight + Insurance</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="13" t="n"/>
+      <c r="O22" s="13" t="n"/>
+      <c r="P22" s="15" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="Q22" s="13" t="n"/>
+      <c r="R22" s="13" t="n"/>
+      <c r="S22" s="13" t="n"/>
+      <c r="T22" s="13" t="n"/>
+      <c r="U22" s="13" t="n"/>
+      <c r="V22" s="13" t="n"/>
+      <c r="W22" s="13" t="n"/>
+      <c r="X22" s="13" t="n"/>
+      <c r="Y22" s="13" t="n"/>
+      <c r="Z22" s="13" t="n"/>
+      <c r="AA22" s="13" t="n"/>
+      <c r="AB22" s="13" t="n"/>
+      <c r="AC22" s="13" t="n"/>
+      <c r="AD22" s="13" t="n"/>
+      <c r="AE22" s="13" t="n"/>
+      <c r="AF22" s="13" t="n"/>
+      <c r="AG22" s="13" t="n"/>
+      <c r="AH22" s="13" t="n"/>
+      <c r="AI22" s="13" t="n"/>
+      <c r="AJ22" s="13" t="n"/>
+      <c r="AK22" s="13" t="n"/>
+    </row>
     <row r="23">
-      <c r="A23" s="14" t="n"/>
-      <c r="B23" s="14" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="14" t="n"/>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-      <c r="H23" s="14" t="n"/>
-      <c r="I23" s="14" t="n"/>
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="13" t="n"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>DUTY ESTIMATION (Classification Cross-Check)</t>
-        </is>
-      </c>
-      <c r="K23" s="14" t="n"/>
-      <c r="L23" s="14" t="n"/>
-      <c r="M23" s="14" t="n"/>
-      <c r="N23" s="14" t="n"/>
-      <c r="O23" s="14" t="n"/>
-      <c r="P23" s="14" t="n"/>
-      <c r="Q23" s="14" t="n"/>
-      <c r="R23" s="14" t="n"/>
-      <c r="S23" s="14" t="n"/>
-      <c r="T23" s="14" t="n"/>
-      <c r="U23" s="14" t="n"/>
-      <c r="V23" s="14" t="n"/>
-      <c r="W23" s="14" t="n"/>
-      <c r="X23" s="14" t="n"/>
-      <c r="Y23" s="14" t="n"/>
-      <c r="Z23" s="14" t="n"/>
-      <c r="AA23" s="14" t="n"/>
-      <c r="AB23" s="14" t="n"/>
-      <c r="AC23" s="14" t="n"/>
-      <c r="AD23" s="14" t="n"/>
-      <c r="AE23" s="14" t="n"/>
-      <c r="AF23" s="14" t="n"/>
-      <c r="AG23" s="14" t="n"/>
-      <c r="AH23" s="14" t="n"/>
-      <c r="AI23" s="14" t="n"/>
-      <c r="AJ23" s="14" t="n"/>
-      <c r="AK23" s="14" t="n"/>
+          <t>CIF (XCD) = CIF × 2.7169</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n"/>
+      <c r="L23" s="13" t="n"/>
+      <c r="M23" s="13" t="n"/>
+      <c r="N23" s="13" t="n"/>
+      <c r="O23" s="13" t="n"/>
+      <c r="P23" s="15" t="n">
+        <v>115.71</v>
+      </c>
+      <c r="Q23" s="13" t="n"/>
+      <c r="R23" s="13" t="n"/>
+      <c r="S23" s="13" t="n"/>
+      <c r="T23" s="13" t="n"/>
+      <c r="U23" s="13" t="n"/>
+      <c r="V23" s="13" t="n"/>
+      <c r="W23" s="13" t="n"/>
+      <c r="X23" s="13" t="n"/>
+      <c r="Y23" s="13" t="n"/>
+      <c r="Z23" s="13" t="n"/>
+      <c r="AA23" s="13" t="n"/>
+      <c r="AB23" s="13" t="n"/>
+      <c r="AC23" s="13" t="n"/>
+      <c r="AD23" s="13" t="n"/>
+      <c r="AE23" s="13" t="n"/>
+      <c r="AF23" s="13" t="n"/>
+      <c r="AG23" s="13" t="n"/>
+      <c r="AH23" s="13" t="n"/>
+      <c r="AI23" s="13" t="n"/>
+      <c r="AJ23" s="13" t="n"/>
+      <c r="AK23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n"/>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>CIF (USD) = InvTotal + Freight + Insurance</t>
-        </is>
-      </c>
-      <c r="K24" s="15" t="n"/>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q24" s="15" t="n"/>
-      <c r="R24" s="15" t="n"/>
-      <c r="S24" s="15" t="n"/>
-      <c r="T24" s="15" t="n"/>
-      <c r="U24" s="15" t="n"/>
-      <c r="V24" s="15" t="n"/>
-      <c r="W24" s="15" t="n"/>
-      <c r="X24" s="15" t="n"/>
-      <c r="Y24" s="15" t="n"/>
-      <c r="Z24" s="15" t="n"/>
-      <c r="AA24" s="15" t="n"/>
-      <c r="AB24" s="15" t="n"/>
-      <c r="AC24" s="15" t="n"/>
-      <c r="AD24" s="15" t="n"/>
-      <c r="AE24" s="15" t="n"/>
-      <c r="AF24" s="15" t="n"/>
-      <c r="AG24" s="15" t="n"/>
-      <c r="AH24" s="15" t="n"/>
-      <c r="AI24" s="15" t="n"/>
-      <c r="AJ24" s="15" t="n"/>
-      <c r="AK24" s="15" t="n"/>
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="13" t="n"/>
+      <c r="I24" s="13" t="n"/>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>CET (weighted avg 9.2%)</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n"/>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="13" t="n"/>
+      <c r="N24" s="13" t="n"/>
+      <c r="O24" s="13" t="n"/>
+      <c r="P24" s="15" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="Q24" s="13" t="n"/>
+      <c r="R24" s="13" t="n"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="13" t="n"/>
+      <c r="U24" s="13" t="n"/>
+      <c r="V24" s="13" t="n"/>
+      <c r="W24" s="13" t="n"/>
+      <c r="X24" s="13" t="n"/>
+      <c r="Y24" s="13" t="n"/>
+      <c r="Z24" s="13" t="n"/>
+      <c r="AA24" s="13" t="n"/>
+      <c r="AB24" s="13" t="n"/>
+      <c r="AC24" s="13" t="n"/>
+      <c r="AD24" s="13" t="n"/>
+      <c r="AE24" s="13" t="n"/>
+      <c r="AF24" s="13" t="n"/>
+      <c r="AG24" s="13" t="n"/>
+      <c r="AH24" s="13" t="n"/>
+      <c r="AI24" s="13" t="n"/>
+      <c r="AJ24" s="13" t="n"/>
+      <c r="AK24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n"/>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
-      <c r="H25" s="15" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>CIF (XCD) = CIF × 2.7169</t>
-        </is>
-      </c>
-      <c r="K25" s="15" t="n"/>
-      <c r="L25" s="15" t="n"/>
-      <c r="M25" s="15" t="n"/>
-      <c r="N25" s="15" t="n"/>
-      <c r="O25" s="15" t="n"/>
-      <c r="P25" s="17" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="Q25" s="15" t="n"/>
-      <c r="R25" s="15" t="n"/>
-      <c r="S25" s="15" t="n"/>
-      <c r="T25" s="15" t="n"/>
-      <c r="U25" s="15" t="n"/>
-      <c r="V25" s="15" t="n"/>
-      <c r="W25" s="15" t="n"/>
-      <c r="X25" s="15" t="n"/>
-      <c r="Y25" s="15" t="n"/>
-      <c r="Z25" s="15" t="n"/>
-      <c r="AA25" s="15" t="n"/>
-      <c r="AB25" s="15" t="n"/>
-      <c r="AC25" s="15" t="n"/>
-      <c r="AD25" s="15" t="n"/>
-      <c r="AE25" s="15" t="n"/>
-      <c r="AF25" s="15" t="n"/>
-      <c r="AG25" s="15" t="n"/>
-      <c r="AH25" s="15" t="n"/>
-      <c r="AI25" s="15" t="n"/>
-      <c r="AJ25" s="15" t="n"/>
-      <c r="AK25" s="15" t="n"/>
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ 64031900: 10% CET (85% of value)</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="13" t="n"/>
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="13" t="n"/>
+      <c r="O25" s="13" t="n"/>
+      <c r="P25" s="15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q25" s="13" t="n"/>
+      <c r="R25" s="13" t="n"/>
+      <c r="S25" s="13" t="n"/>
+      <c r="T25" s="13" t="n"/>
+      <c r="U25" s="13" t="n"/>
+      <c r="V25" s="13" t="n"/>
+      <c r="W25" s="13" t="n"/>
+      <c r="X25" s="13" t="n"/>
+      <c r="Y25" s="13" t="n"/>
+      <c r="Z25" s="13" t="n"/>
+      <c r="AA25" s="13" t="n"/>
+      <c r="AB25" s="13" t="n"/>
+      <c r="AC25" s="13" t="n"/>
+      <c r="AD25" s="13" t="n"/>
+      <c r="AE25" s="13" t="n"/>
+      <c r="AF25" s="13" t="n"/>
+      <c r="AG25" s="13" t="n"/>
+      <c r="AH25" s="13" t="n"/>
+      <c r="AI25" s="13" t="n"/>
+      <c r="AJ25" s="13" t="n"/>
+      <c r="AK25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>CET (weighted avg 20.0%)</t>
-        </is>
-      </c>
-      <c r="K26" s="15" t="n"/>
-      <c r="L26" s="15" t="n"/>
-      <c r="M26" s="15" t="n"/>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="15" t="n"/>
-      <c r="P26" s="17" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="Q26" s="15" t="n"/>
-      <c r="R26" s="15" t="n"/>
-      <c r="S26" s="15" t="n"/>
-      <c r="T26" s="15" t="n"/>
-      <c r="U26" s="15" t="n"/>
-      <c r="V26" s="15" t="n"/>
-      <c r="W26" s="15" t="n"/>
-      <c r="X26" s="15" t="n"/>
-      <c r="Y26" s="15" t="n"/>
-      <c r="Z26" s="15" t="n"/>
-      <c r="AA26" s="15" t="n"/>
-      <c r="AB26" s="15" t="n"/>
-      <c r="AC26" s="15" t="n"/>
-      <c r="AD26" s="15" t="n"/>
-      <c r="AE26" s="15" t="n"/>
-      <c r="AF26" s="15" t="n"/>
-      <c r="AG26" s="15" t="n"/>
-      <c r="AH26" s="15" t="n"/>
-      <c r="AI26" s="15" t="n"/>
-      <c r="AJ26" s="15" t="n"/>
-      <c r="AK26" s="15" t="n"/>
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="13" t="n"/>
+      <c r="I26" s="13" t="n"/>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ 76169990: 5% CET (15% of value)</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="13" t="n"/>
+      <c r="P26" s="15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q26" s="13" t="n"/>
+      <c r="R26" s="13" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="13" t="n"/>
+      <c r="U26" s="13" t="n"/>
+      <c r="V26" s="13" t="n"/>
+      <c r="W26" s="13" t="n"/>
+      <c r="X26" s="13" t="n"/>
+      <c r="Y26" s="13" t="n"/>
+      <c r="Z26" s="13" t="n"/>
+      <c r="AA26" s="13" t="n"/>
+      <c r="AB26" s="13" t="n"/>
+      <c r="AC26" s="13" t="n"/>
+      <c r="AD26" s="13" t="n"/>
+      <c r="AE26" s="13" t="n"/>
+      <c r="AF26" s="13" t="n"/>
+      <c r="AG26" s="13" t="n"/>
+      <c r="AH26" s="13" t="n"/>
+      <c r="AI26" s="13" t="n"/>
+      <c r="AJ26" s="13" t="n"/>
+      <c r="AK26" s="13" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n"/>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="15" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └ 00000000: 20% CET (0% of value)</t>
-        </is>
-      </c>
-      <c r="K27" s="15" t="n"/>
-      <c r="L27" s="15" t="n"/>
-      <c r="M27" s="15" t="n"/>
-      <c r="N27" s="15" t="n"/>
-      <c r="O27" s="15" t="n"/>
-      <c r="P27" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="15" t="n"/>
-      <c r="R27" s="15" t="n"/>
-      <c r="S27" s="15" t="n"/>
-      <c r="T27" s="15" t="n"/>
-      <c r="U27" s="15" t="n"/>
-      <c r="V27" s="15" t="n"/>
-      <c r="W27" s="15" t="n"/>
-      <c r="X27" s="15" t="n"/>
-      <c r="Y27" s="15" t="n"/>
-      <c r="Z27" s="15" t="n"/>
-      <c r="AA27" s="15" t="n"/>
-      <c r="AB27" s="15" t="n"/>
-      <c r="AC27" s="15" t="n"/>
-      <c r="AD27" s="15" t="n"/>
-      <c r="AE27" s="15" t="n"/>
-      <c r="AF27" s="15" t="n"/>
-      <c r="AG27" s="15" t="n"/>
-      <c r="AH27" s="15" t="n"/>
-      <c r="AI27" s="15" t="n"/>
-      <c r="AJ27" s="15" t="n"/>
-      <c r="AK27" s="15" t="n"/>
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>CSC (6%)</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n"/>
+      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="13" t="n"/>
+      <c r="N27" s="13" t="n"/>
+      <c r="O27" s="13" t="n"/>
+      <c r="P27" s="15" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="Q27" s="13" t="n"/>
+      <c r="R27" s="13" t="n"/>
+      <c r="S27" s="13" t="n"/>
+      <c r="T27" s="13" t="n"/>
+      <c r="U27" s="13" t="n"/>
+      <c r="V27" s="13" t="n"/>
+      <c r="W27" s="13" t="n"/>
+      <c r="X27" s="13" t="n"/>
+      <c r="Y27" s="13" t="n"/>
+      <c r="Z27" s="13" t="n"/>
+      <c r="AA27" s="13" t="n"/>
+      <c r="AB27" s="13" t="n"/>
+      <c r="AC27" s="13" t="n"/>
+      <c r="AD27" s="13" t="n"/>
+      <c r="AE27" s="13" t="n"/>
+      <c r="AF27" s="13" t="n"/>
+      <c r="AG27" s="13" t="n"/>
+      <c r="AH27" s="13" t="n"/>
+      <c r="AI27" s="13" t="n"/>
+      <c r="AJ27" s="13" t="n"/>
+      <c r="AK27" s="13" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └ 99999999: 20% CET (0% of value)</t>
-        </is>
-      </c>
-      <c r="K28" s="15" t="n"/>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="n"/>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="15" t="n"/>
-      <c r="P28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="15" t="n"/>
-      <c r="R28" s="15" t="n"/>
-      <c r="S28" s="15" t="n"/>
-      <c r="T28" s="15" t="n"/>
-      <c r="U28" s="15" t="n"/>
-      <c r="V28" s="15" t="n"/>
-      <c r="W28" s="15" t="n"/>
-      <c r="X28" s="15" t="n"/>
-      <c r="Y28" s="15" t="n"/>
-      <c r="Z28" s="15" t="n"/>
-      <c r="AA28" s="15" t="n"/>
-      <c r="AB28" s="15" t="n"/>
-      <c r="AC28" s="15" t="n"/>
-      <c r="AD28" s="15" t="n"/>
-      <c r="AE28" s="15" t="n"/>
-      <c r="AF28" s="15" t="n"/>
-      <c r="AG28" s="15" t="n"/>
-      <c r="AH28" s="15" t="n"/>
-      <c r="AI28" s="15" t="n"/>
-      <c r="AJ28" s="15" t="n"/>
-      <c r="AK28" s="15" t="n"/>
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="13" t="n"/>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>VAT (15%) on CIF+CET+CSC</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="13" t="n"/>
+      <c r="O28" s="13" t="n"/>
+      <c r="P28" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q28" s="13" t="n"/>
+      <c r="R28" s="13" t="n"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="13" t="n"/>
+      <c r="U28" s="13" t="n"/>
+      <c r="V28" s="13" t="n"/>
+      <c r="W28" s="13" t="n"/>
+      <c r="X28" s="13" t="n"/>
+      <c r="Y28" s="13" t="n"/>
+      <c r="Z28" s="13" t="n"/>
+      <c r="AA28" s="13" t="n"/>
+      <c r="AB28" s="13" t="n"/>
+      <c r="AC28" s="13" t="n"/>
+      <c r="AD28" s="13" t="n"/>
+      <c r="AE28" s="13" t="n"/>
+      <c r="AF28" s="13" t="n"/>
+      <c r="AG28" s="13" t="n"/>
+      <c r="AH28" s="13" t="n"/>
+      <c r="AI28" s="13" t="n"/>
+      <c r="AJ28" s="13" t="n"/>
+      <c r="AK28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n"/>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="15" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>CSC (6%)</t>
-        </is>
-      </c>
-      <c r="K29" s="15" t="n"/>
-      <c r="L29" s="15" t="n"/>
-      <c r="M29" s="15" t="n"/>
-      <c r="N29" s="15" t="n"/>
-      <c r="O29" s="15" t="n"/>
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="16" t="n"/>
+      <c r="I29" s="16" t="n"/>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>ESTIMATED TOTAL DUTIES</t>
+        </is>
+      </c>
+      <c r="K29" s="16" t="n"/>
+      <c r="L29" s="16" t="n"/>
+      <c r="M29" s="16" t="n"/>
+      <c r="N29" s="16" t="n"/>
+      <c r="O29" s="16" t="n"/>
       <c r="P29" s="17" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="Q29" s="15" t="n"/>
-      <c r="R29" s="15" t="n"/>
-      <c r="S29" s="15" t="n"/>
-      <c r="T29" s="15" t="n"/>
-      <c r="U29" s="15" t="n"/>
-      <c r="V29" s="15" t="n"/>
-      <c r="W29" s="15" t="n"/>
-      <c r="X29" s="15" t="n"/>
-      <c r="Y29" s="15" t="n"/>
-      <c r="Z29" s="15" t="n"/>
-      <c r="AA29" s="15" t="n"/>
-      <c r="AB29" s="15" t="n"/>
-      <c r="AC29" s="15" t="n"/>
-      <c r="AD29" s="15" t="n"/>
-      <c r="AE29" s="15" t="n"/>
-      <c r="AF29" s="15" t="n"/>
-      <c r="AG29" s="15" t="n"/>
-      <c r="AH29" s="15" t="n"/>
-      <c r="AI29" s="15" t="n"/>
-      <c r="AJ29" s="15" t="n"/>
-      <c r="AK29" s="15" t="n"/>
+        <v>37.63</v>
+      </c>
+      <c r="Q29" s="16" t="n"/>
+      <c r="R29" s="16" t="n"/>
+      <c r="S29" s="16" t="n"/>
+      <c r="T29" s="16" t="n"/>
+      <c r="U29" s="16" t="n"/>
+      <c r="V29" s="16" t="n"/>
+      <c r="W29" s="16" t="n"/>
+      <c r="X29" s="16" t="n"/>
+      <c r="Y29" s="16" t="n"/>
+      <c r="Z29" s="16" t="n"/>
+      <c r="AA29" s="16" t="n"/>
+      <c r="AB29" s="16" t="n"/>
+      <c r="AC29" s="16" t="n"/>
+      <c r="AD29" s="16" t="n"/>
+      <c r="AE29" s="16" t="n"/>
+      <c r="AF29" s="16" t="n"/>
+      <c r="AG29" s="16" t="n"/>
+      <c r="AH29" s="16" t="n"/>
+      <c r="AI29" s="16" t="n"/>
+      <c r="AJ29" s="16" t="n"/>
+      <c r="AK29" s="16" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>VAT (15%) on CIF+CET+CSC</t>
-        </is>
-      </c>
-      <c r="K30" s="15" t="n"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="15" t="n"/>
-      <c r="N30" s="15" t="n"/>
-      <c r="O30" s="15" t="n"/>
-      <c r="P30" s="17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Q30" s="15" t="n"/>
-      <c r="R30" s="15" t="n"/>
-      <c r="S30" s="15" t="n"/>
-      <c r="T30" s="15" t="n"/>
-      <c r="U30" s="15" t="n"/>
-      <c r="V30" s="15" t="n"/>
-      <c r="W30" s="15" t="n"/>
-      <c r="X30" s="15" t="n"/>
-      <c r="Y30" s="15" t="n"/>
-      <c r="Z30" s="15" t="n"/>
-      <c r="AA30" s="15" t="n"/>
-      <c r="AB30" s="15" t="n"/>
-      <c r="AC30" s="15" t="n"/>
-      <c r="AD30" s="15" t="n"/>
-      <c r="AE30" s="15" t="n"/>
-      <c r="AF30" s="15" t="n"/>
-      <c r="AG30" s="15" t="n"/>
-      <c r="AH30" s="15" t="n"/>
-      <c r="AI30" s="15" t="n"/>
-      <c r="AJ30" s="15" t="n"/>
-      <c r="AK30" s="15" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="n"/>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="18" t="n"/>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="14" t="inlineStr">
-        <is>
-          <t>ESTIMATED TOTAL DUTIES</t>
-        </is>
-      </c>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="18" t="n"/>
-      <c r="N31" s="18" t="n"/>
-      <c r="O31" s="18" t="n"/>
-      <c r="P31" s="19" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="Q31" s="18" t="n"/>
-      <c r="R31" s="18" t="n"/>
-      <c r="S31" s="18" t="n"/>
-      <c r="T31" s="18" t="n"/>
-      <c r="U31" s="18" t="n"/>
-      <c r="V31" s="18" t="n"/>
-      <c r="W31" s="18" t="n"/>
-      <c r="X31" s="18" t="n"/>
-      <c r="Y31" s="18" t="n"/>
-      <c r="Z31" s="18" t="n"/>
-      <c r="AA31" s="18" t="n"/>
-      <c r="AB31" s="18" t="n"/>
-      <c r="AC31" s="18" t="n"/>
-      <c r="AD31" s="18" t="n"/>
-      <c r="AE31" s="18" t="n"/>
-      <c r="AF31" s="18" t="n"/>
-      <c r="AG31" s="18" t="n"/>
-      <c r="AH31" s="18" t="n"/>
-      <c r="AI31" s="18" t="n"/>
-      <c r="AJ31" s="18" t="n"/>
-      <c r="AK31" s="18" t="n"/>
-    </row>
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="13" t="n"/>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Effective Duty Rate</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n"/>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="13" t="n"/>
+      <c r="N30" s="13" t="n"/>
+      <c r="O30" s="13" t="n"/>
+      <c r="P30" s="18" t="n">
+        <v>0.3252095756632962</v>
+      </c>
+      <c r="Q30" s="13" t="n"/>
+      <c r="R30" s="13" t="n"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="13" t="n"/>
+      <c r="U30" s="13" t="n"/>
+      <c r="V30" s="13" t="n"/>
+      <c r="W30" s="13" t="n"/>
+      <c r="X30" s="13" t="n"/>
+      <c r="Y30" s="13" t="n"/>
+      <c r="Z30" s="13" t="n"/>
+      <c r="AA30" s="13" t="n"/>
+      <c r="AB30" s="13" t="n"/>
+      <c r="AC30" s="13" t="n"/>
+      <c r="AD30" s="13" t="n"/>
+      <c r="AE30" s="13" t="n"/>
+      <c r="AF30" s="13" t="n"/>
+      <c r="AG30" s="13" t="n"/>
+      <c r="AH30" s="13" t="n"/>
+      <c r="AI30" s="13" t="n"/>
+      <c r="AJ30" s="13" t="n"/>
+      <c r="AK30" s="13" t="n"/>
+    </row>
+    <row r="31"/>
     <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="15" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="15" t="n"/>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
-      <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>Effective Duty Rate</t>
-        </is>
-      </c>
-      <c r="K32" s="15" t="n"/>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="15" t="n"/>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="15" t="n"/>
-      <c r="P32" s="20" t="n">
-        <v>0.449079754601227</v>
-      </c>
-      <c r="Q32" s="15" t="n"/>
-      <c r="R32" s="15" t="n"/>
-      <c r="S32" s="15" t="n"/>
-      <c r="T32" s="15" t="n"/>
-      <c r="U32" s="15" t="n"/>
-      <c r="V32" s="15" t="n"/>
-      <c r="W32" s="15" t="n"/>
-      <c r="X32" s="15" t="n"/>
-      <c r="Y32" s="15" t="n"/>
-      <c r="Z32" s="15" t="n"/>
-      <c r="AA32" s="15" t="n"/>
-      <c r="AB32" s="15" t="n"/>
-      <c r="AC32" s="15" t="n"/>
-      <c r="AD32" s="15" t="n"/>
-      <c r="AE32" s="15" t="n"/>
-      <c r="AF32" s="15" t="n"/>
-      <c r="AG32" s="15" t="n"/>
-      <c r="AH32" s="15" t="n"/>
-      <c r="AI32" s="15" t="n"/>
-      <c r="AJ32" s="15" t="n"/>
-      <c r="AK32" s="15" t="n"/>
-    </row>
-    <row r="33"/>
+      <c r="A32" s="19" t="n"/>
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="19" t="n"/>
+      <c r="H32" s="19" t="n"/>
+      <c r="I32" s="19" t="n"/>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>Items on other declaration(s) (1 items)</t>
+        </is>
+      </c>
+      <c r="K32" s="19" t="n"/>
+      <c r="L32" s="19" t="n"/>
+      <c r="M32" s="19" t="n"/>
+      <c r="N32" s="19" t="n"/>
+      <c r="O32" s="19" t="n"/>
+      <c r="P32" s="20" t="n"/>
+      <c r="Q32" s="19" t="n"/>
+      <c r="R32" s="19" t="n"/>
+      <c r="S32" s="19" t="n"/>
+      <c r="T32" s="19" t="n"/>
+      <c r="U32" s="19" t="n"/>
+      <c r="V32" s="19" t="n"/>
+      <c r="W32" s="19" t="n"/>
+      <c r="X32" s="19" t="n"/>
+      <c r="Y32" s="19" t="n"/>
+      <c r="Z32" s="19" t="n"/>
+      <c r="AA32" s="19" t="n"/>
+      <c r="AB32" s="19" t="n"/>
+      <c r="AC32" s="19" t="n"/>
+      <c r="AD32" s="19" t="n"/>
+      <c r="AE32" s="19" t="n"/>
+      <c r="AF32" s="19" t="n"/>
+      <c r="AG32" s="19" t="n"/>
+      <c r="AH32" s="19" t="n"/>
+      <c r="AI32" s="19" t="n"/>
+      <c r="AJ32" s="19" t="n"/>
+      <c r="AK32" s="19" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="n"/>
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>Fans</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="inlineStr">
+        <is>
+          <t>84145900</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="19" t="n"/>
+      <c r="J33" s="19" t="inlineStr">
+        <is>
+          <t>QUETTERLEE Replacement Internal Cooling Fan for Sony PS4 Fan ps4 CUH-1000 CUH... (1 items)</t>
+        </is>
+      </c>
+      <c r="K33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="19" t="n"/>
+      <c r="N33" s="19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O33" s="20" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="P33" s="20" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="Q33" s="20" t="n"/>
+      <c r="R33" s="20" t="n"/>
+      <c r="S33" s="20" t="n"/>
+      <c r="T33" s="20" t="n"/>
+      <c r="U33" s="20" t="n"/>
+      <c r="V33" s="20" t="n"/>
+      <c r="W33" s="20" t="n"/>
+      <c r="X33" s="19" t="n"/>
+      <c r="Y33" s="19" t="n"/>
+      <c r="Z33" s="19" t="n"/>
+      <c r="AA33" s="19" t="n"/>
+      <c r="AB33" s="19" t="n"/>
+      <c r="AC33" s="19" t="n"/>
+      <c r="AD33" s="19" t="n"/>
+      <c r="AE33" s="19" t="n"/>
+      <c r="AF33" s="19" t="n"/>
+      <c r="AG33" s="19" t="n"/>
+      <c r="AH33" s="19" t="n"/>
+      <c r="AI33" s="19" t="n"/>
+      <c r="AJ33" s="19" t="n"/>
+      <c r="AK33" s="19" t="n"/>
+    </row>
     <row r="34">
       <c r="A34" s="21" t="n"/>
       <c r="B34" s="21" t="n"/>
@@ -2104,20 +2159,34 @@
       <c r="F34" s="21" t="n"/>
       <c r="G34" s="21" t="n"/>
       <c r="H34" s="21" t="n"/>
-      <c r="I34" s="21" t="n"/>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>AMZ-2</t>
+        </is>
+      </c>
       <c r="J34" s="21" t="inlineStr">
         <is>
-          <t>Items on other declaration(s) (1 items)</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="n"/>
+          <t>QUETTERLEE Replacement Internal Cooling Fan for Sony PS4 Fan ps4 CUH-1000 CUH...</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="n">
+        <v>1</v>
+      </c>
       <c r="L34" s="21" t="n"/>
       <c r="M34" s="21" t="n"/>
-      <c r="N34" s="21" t="n"/>
-      <c r="O34" s="21" t="n"/>
-      <c r="P34" s="22" t="n"/>
-      <c r="Q34" s="21" t="n"/>
-      <c r="R34" s="21" t="n"/>
+      <c r="N34" s="21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O34" s="22" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="P34" s="22" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="Q34" s="22" t="n"/>
+      <c r="R34" s="22" t="n"/>
       <c r="S34" s="21" t="n"/>
       <c r="T34" s="21" t="n"/>
       <c r="U34" s="21" t="n"/>
@@ -2139,65 +2208,49 @@
       <c r="AK34" s="21" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="n"/>
-      <c r="B35" s="21" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>Unclassifiable / Non-physical goods</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
-        <is>
-          <t>49090090</t>
-        </is>
-      </c>
-      <c r="G35" s="21" t="n"/>
-      <c r="H35" s="21" t="n"/>
-      <c r="I35" s="21" t="n"/>
-      <c r="J35" s="21" t="inlineStr">
-        <is>
-          <t>Gift Card Amount: - (1 items)</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="21" t="n"/>
-      <c r="N35" s="21" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O35" s="22" t="n">
-        <v>51.58</v>
-      </c>
-      <c r="P35" s="22" t="n">
-        <v>51.58</v>
-      </c>
-      <c r="Q35" s="22" t="n"/>
-      <c r="R35" s="22" t="n"/>
-      <c r="S35" s="22" t="n"/>
-      <c r="T35" s="22" t="n"/>
-      <c r="U35" s="22" t="n"/>
-      <c r="V35" s="22" t="n"/>
-      <c r="W35" s="22" t="n"/>
-      <c r="X35" s="21" t="n"/>
-      <c r="Y35" s="21" t="n"/>
-      <c r="Z35" s="21" t="n"/>
-      <c r="AA35" s="21" t="n"/>
-      <c r="AB35" s="21" t="n"/>
-      <c r="AC35" s="21" t="n"/>
-      <c r="AD35" s="21" t="n"/>
-      <c r="AE35" s="21" t="n"/>
-      <c r="AF35" s="21" t="n"/>
-      <c r="AG35" s="21" t="n"/>
-      <c r="AH35" s="21" t="n"/>
-      <c r="AI35" s="21" t="n"/>
-      <c r="AJ35" s="21" t="n"/>
-      <c r="AK35" s="21" t="n"/>
+      <c r="A35" s="23" t="n"/>
+      <c r="B35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="23" t="n"/>
+      <c r="I35" s="23" t="n"/>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>REFERENCE SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="n"/>
+      <c r="L35" s="23" t="n"/>
+      <c r="M35" s="23" t="n"/>
+      <c r="N35" s="23" t="n"/>
+      <c r="O35" s="23" t="n"/>
+      <c r="P35" s="24" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="Q35" s="23" t="n"/>
+      <c r="R35" s="23" t="n"/>
+      <c r="S35" s="23" t="n"/>
+      <c r="T35" s="23" t="n"/>
+      <c r="U35" s="23" t="n"/>
+      <c r="V35" s="23" t="n"/>
+      <c r="W35" s="23" t="n"/>
+      <c r="X35" s="23" t="n"/>
+      <c r="Y35" s="23" t="n"/>
+      <c r="Z35" s="23" t="n"/>
+      <c r="AA35" s="23" t="n"/>
+      <c r="AB35" s="23" t="n"/>
+      <c r="AC35" s="23" t="n"/>
+      <c r="AD35" s="23" t="n"/>
+      <c r="AE35" s="23" t="n"/>
+      <c r="AF35" s="23" t="n"/>
+      <c r="AG35" s="23" t="n"/>
+      <c r="AH35" s="23" t="n"/>
+      <c r="AI35" s="23" t="n"/>
+      <c r="AJ35" s="23" t="n"/>
+      <c r="AK35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="23" t="n"/>
@@ -2208,34 +2261,22 @@
       <c r="F36" s="23" t="n"/>
       <c r="G36" s="23" t="n"/>
       <c r="H36" s="23" t="n"/>
-      <c r="I36" s="23" t="inlineStr">
-        <is>
-          <t>TEMU-2</t>
-        </is>
-      </c>
+      <c r="I36" s="23" t="n"/>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>Gift Card Amount: -</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v>1</v>
-      </c>
+          <t>REFERENCE FREIGHT</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="n"/>
       <c r="L36" s="23" t="n"/>
       <c r="M36" s="23" t="n"/>
-      <c r="N36" s="23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="O36" s="24" t="n">
-        <v>51.58</v>
-      </c>
+      <c r="N36" s="23" t="n"/>
+      <c r="O36" s="23" t="n"/>
       <c r="P36" s="24" t="n">
-        <v>51.58</v>
-      </c>
-      <c r="Q36" s="24" t="n"/>
-      <c r="R36" s="24" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="Q36" s="23" t="n"/>
+      <c r="R36" s="23" t="n"/>
       <c r="S36" s="23" t="n"/>
       <c r="T36" s="23" t="n"/>
       <c r="U36" s="23" t="n"/>
@@ -2257,734 +2298,644 @@
       <c r="AK36" s="23" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="25" t="n"/>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="25" t="n"/>
-      <c r="D37" s="25" t="n"/>
-      <c r="E37" s="25" t="n"/>
-      <c r="F37" s="25" t="n"/>
-      <c r="G37" s="25" t="n"/>
-      <c r="H37" s="25" t="n"/>
-      <c r="I37" s="25" t="n"/>
-      <c r="J37" s="25" t="inlineStr">
-        <is>
-          <t>REFERENCE SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="K37" s="25" t="n"/>
-      <c r="L37" s="25" t="n"/>
-      <c r="M37" s="25" t="n"/>
-      <c r="N37" s="25" t="n"/>
-      <c r="O37" s="25" t="n"/>
-      <c r="P37" s="26" t="n">
-        <v>51.58</v>
-      </c>
-      <c r="Q37" s="25" t="n"/>
-      <c r="R37" s="25" t="n"/>
-      <c r="S37" s="25" t="n"/>
-      <c r="T37" s="25" t="n"/>
-      <c r="U37" s="25" t="n"/>
-      <c r="V37" s="25" t="n"/>
-      <c r="W37" s="25" t="n"/>
-      <c r="X37" s="25" t="n"/>
-      <c r="Y37" s="25" t="n"/>
-      <c r="Z37" s="25" t="n"/>
-      <c r="AA37" s="25" t="n"/>
-      <c r="AB37" s="25" t="n"/>
-      <c r="AC37" s="25" t="n"/>
-      <c r="AD37" s="25" t="n"/>
-      <c r="AE37" s="25" t="n"/>
-      <c r="AF37" s="25" t="n"/>
-      <c r="AG37" s="25" t="n"/>
-      <c r="AH37" s="25" t="n"/>
-      <c r="AI37" s="25" t="n"/>
-      <c r="AJ37" s="25" t="n"/>
-      <c r="AK37" s="25" t="n"/>
+      <c r="A37" s="23" t="n"/>
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="23" t="n"/>
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="23" t="n"/>
+      <c r="H37" s="23" t="n"/>
+      <c r="I37" s="23" t="n"/>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>REFERENCE INSURANCE</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="n"/>
+      <c r="L37" s="23" t="n"/>
+      <c r="M37" s="23" t="n"/>
+      <c r="N37" s="23" t="n"/>
+      <c r="O37" s="23" t="n"/>
+      <c r="P37" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="23" t="n"/>
+      <c r="R37" s="23" t="n"/>
+      <c r="S37" s="23" t="n"/>
+      <c r="T37" s="23" t="n"/>
+      <c r="U37" s="23" t="n"/>
+      <c r="V37" s="23" t="n"/>
+      <c r="W37" s="23" t="n"/>
+      <c r="X37" s="23" t="n"/>
+      <c r="Y37" s="23" t="n"/>
+      <c r="Z37" s="23" t="n"/>
+      <c r="AA37" s="23" t="n"/>
+      <c r="AB37" s="23" t="n"/>
+      <c r="AC37" s="23" t="n"/>
+      <c r="AD37" s="23" t="n"/>
+      <c r="AE37" s="23" t="n"/>
+      <c r="AF37" s="23" t="n"/>
+      <c r="AG37" s="23" t="n"/>
+      <c r="AH37" s="23" t="n"/>
+      <c r="AI37" s="23" t="n"/>
+      <c r="AJ37" s="23" t="n"/>
+      <c r="AK37" s="23" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="25" t="n"/>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="25" t="n"/>
-      <c r="D38" s="25" t="n"/>
-      <c r="E38" s="25" t="n"/>
-      <c r="F38" s="25" t="n"/>
-      <c r="G38" s="25" t="n"/>
-      <c r="H38" s="25" t="n"/>
-      <c r="I38" s="25" t="n"/>
-      <c r="J38" s="25" t="inlineStr">
-        <is>
-          <t>REFERENCE FREIGHT</t>
-        </is>
-      </c>
-      <c r="K38" s="25" t="n"/>
-      <c r="L38" s="25" t="n"/>
-      <c r="M38" s="25" t="n"/>
-      <c r="N38" s="25" t="n"/>
-      <c r="O38" s="25" t="n"/>
-      <c r="P38" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q38" s="25" t="n"/>
-      <c r="R38" s="25" t="n"/>
-      <c r="S38" s="25" t="n"/>
-      <c r="T38" s="25" t="n"/>
-      <c r="U38" s="25" t="n"/>
-      <c r="V38" s="25" t="n"/>
-      <c r="W38" s="25" t="n"/>
-      <c r="X38" s="25" t="n"/>
-      <c r="Y38" s="25" t="n"/>
-      <c r="Z38" s="25" t="n"/>
-      <c r="AA38" s="25" t="n"/>
-      <c r="AB38" s="25" t="n"/>
-      <c r="AC38" s="25" t="n"/>
-      <c r="AD38" s="25" t="n"/>
-      <c r="AE38" s="25" t="n"/>
-      <c r="AF38" s="25" t="n"/>
-      <c r="AG38" s="25" t="n"/>
-      <c r="AH38" s="25" t="n"/>
-      <c r="AI38" s="25" t="n"/>
-      <c r="AJ38" s="25" t="n"/>
-      <c r="AK38" s="25" t="n"/>
+      <c r="A38" s="23" t="n"/>
+      <c r="B38" s="23" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="23" t="n"/>
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="23" t="n"/>
+      <c r="H38" s="23" t="n"/>
+      <c r="I38" s="23" t="n"/>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>REFERENCE OTHER COST</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="n"/>
+      <c r="L38" s="23" t="n"/>
+      <c r="M38" s="23" t="n"/>
+      <c r="N38" s="23" t="n"/>
+      <c r="O38" s="23" t="n"/>
+      <c r="P38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="23" t="n"/>
+      <c r="R38" s="23" t="n"/>
+      <c r="S38" s="23" t="n"/>
+      <c r="T38" s="23" t="n"/>
+      <c r="U38" s="23" t="n"/>
+      <c r="V38" s="23" t="n"/>
+      <c r="W38" s="23" t="n"/>
+      <c r="X38" s="23" t="n"/>
+      <c r="Y38" s="23" t="n"/>
+      <c r="Z38" s="23" t="n"/>
+      <c r="AA38" s="23" t="n"/>
+      <c r="AB38" s="23" t="n"/>
+      <c r="AC38" s="23" t="n"/>
+      <c r="AD38" s="23" t="n"/>
+      <c r="AE38" s="23" t="n"/>
+      <c r="AF38" s="23" t="n"/>
+      <c r="AG38" s="23" t="n"/>
+      <c r="AH38" s="23" t="n"/>
+      <c r="AI38" s="23" t="n"/>
+      <c r="AJ38" s="23" t="n"/>
+      <c r="AK38" s="23" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="25" t="n"/>
-      <c r="B39" s="25" t="n"/>
-      <c r="C39" s="25" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="25" t="n"/>
-      <c r="G39" s="25" t="n"/>
-      <c r="H39" s="25" t="n"/>
-      <c r="I39" s="25" t="n"/>
-      <c r="J39" s="25" t="inlineStr">
-        <is>
-          <t>REFERENCE INSURANCE</t>
-        </is>
-      </c>
-      <c r="K39" s="25" t="n"/>
-      <c r="L39" s="25" t="n"/>
-      <c r="M39" s="25" t="n"/>
-      <c r="N39" s="25" t="n"/>
-      <c r="O39" s="25" t="n"/>
-      <c r="P39" s="26" t="n">
+      <c r="A39" s="23" t="n"/>
+      <c r="B39" s="23" t="n"/>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="23" t="n"/>
+      <c r="F39" s="23" t="n"/>
+      <c r="G39" s="23" t="n"/>
+      <c r="H39" s="23" t="n"/>
+      <c r="I39" s="23" t="n"/>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>REFERENCE DEDUCTION</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="n"/>
+      <c r="L39" s="23" t="n"/>
+      <c r="M39" s="23" t="n"/>
+      <c r="N39" s="23" t="n"/>
+      <c r="O39" s="23" t="n"/>
+      <c r="P39" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="25" t="n"/>
-      <c r="R39" s="25" t="n"/>
-      <c r="S39" s="25" t="n"/>
-      <c r="T39" s="25" t="n"/>
-      <c r="U39" s="25" t="n"/>
-      <c r="V39" s="25" t="n"/>
-      <c r="W39" s="25" t="n"/>
-      <c r="X39" s="25" t="n"/>
-      <c r="Y39" s="25" t="n"/>
-      <c r="Z39" s="25" t="n"/>
-      <c r="AA39" s="25" t="n"/>
-      <c r="AB39" s="25" t="n"/>
-      <c r="AC39" s="25" t="n"/>
-      <c r="AD39" s="25" t="n"/>
-      <c r="AE39" s="25" t="n"/>
-      <c r="AF39" s="25" t="n"/>
-      <c r="AG39" s="25" t="n"/>
-      <c r="AH39" s="25" t="n"/>
-      <c r="AI39" s="25" t="n"/>
-      <c r="AJ39" s="25" t="n"/>
-      <c r="AK39" s="25" t="n"/>
+      <c r="Q39" s="23" t="n"/>
+      <c r="R39" s="23" t="n"/>
+      <c r="S39" s="23" t="n"/>
+      <c r="T39" s="23" t="n"/>
+      <c r="U39" s="23" t="n"/>
+      <c r="V39" s="23" t="n"/>
+      <c r="W39" s="23" t="n"/>
+      <c r="X39" s="23" t="n"/>
+      <c r="Y39" s="23" t="n"/>
+      <c r="Z39" s="23" t="n"/>
+      <c r="AA39" s="23" t="n"/>
+      <c r="AB39" s="23" t="n"/>
+      <c r="AC39" s="23" t="n"/>
+      <c r="AD39" s="23" t="n"/>
+      <c r="AE39" s="23" t="n"/>
+      <c r="AF39" s="23" t="n"/>
+      <c r="AG39" s="23" t="n"/>
+      <c r="AH39" s="23" t="n"/>
+      <c r="AI39" s="23" t="n"/>
+      <c r="AJ39" s="23" t="n"/>
+      <c r="AK39" s="23" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="n"/>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="25" t="n"/>
-      <c r="D40" s="25" t="n"/>
-      <c r="E40" s="25" t="n"/>
-      <c r="F40" s="25" t="n"/>
-      <c r="G40" s="25" t="n"/>
-      <c r="H40" s="25" t="n"/>
-      <c r="I40" s="25" t="n"/>
-      <c r="J40" s="25" t="inlineStr">
-        <is>
-          <t>REFERENCE OTHER COST</t>
-        </is>
-      </c>
-      <c r="K40" s="25" t="n"/>
-      <c r="L40" s="25" t="n"/>
-      <c r="M40" s="25" t="n"/>
-      <c r="N40" s="25" t="n"/>
-      <c r="O40" s="25" t="n"/>
-      <c r="P40" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="25" t="n"/>
-      <c r="R40" s="25" t="n"/>
-      <c r="S40" s="25" t="n"/>
-      <c r="T40" s="25" t="n"/>
-      <c r="U40" s="25" t="n"/>
-      <c r="V40" s="25" t="n"/>
-      <c r="W40" s="25" t="n"/>
-      <c r="X40" s="25" t="n"/>
-      <c r="Y40" s="25" t="n"/>
-      <c r="Z40" s="25" t="n"/>
-      <c r="AA40" s="25" t="n"/>
-      <c r="AB40" s="25" t="n"/>
-      <c r="AC40" s="25" t="n"/>
-      <c r="AD40" s="25" t="n"/>
-      <c r="AE40" s="25" t="n"/>
-      <c r="AF40" s="25" t="n"/>
-      <c r="AG40" s="25" t="n"/>
-      <c r="AH40" s="25" t="n"/>
-      <c r="AI40" s="25" t="n"/>
-      <c r="AJ40" s="25" t="n"/>
-      <c r="AK40" s="25" t="n"/>
+      <c r="A40" s="23" t="n"/>
+      <c r="B40" s="23" t="n"/>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="23" t="n"/>
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="23" t="n"/>
+      <c r="H40" s="23" t="n"/>
+      <c r="I40" s="23" t="n"/>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>REFERENCE ADJUSTMENTS</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="n"/>
+      <c r="L40" s="23" t="n"/>
+      <c r="M40" s="23" t="n"/>
+      <c r="N40" s="23" t="n"/>
+      <c r="O40" s="23" t="n"/>
+      <c r="P40" s="24">
+        <f>P36+P37+P38-P39</f>
+        <v/>
+      </c>
+      <c r="Q40" s="23" t="n"/>
+      <c r="R40" s="23" t="n"/>
+      <c r="S40" s="23" t="n"/>
+      <c r="T40" s="23" t="n"/>
+      <c r="U40" s="23" t="n"/>
+      <c r="V40" s="23" t="n"/>
+      <c r="W40" s="23" t="n"/>
+      <c r="X40" s="23" t="n"/>
+      <c r="Y40" s="23" t="n"/>
+      <c r="Z40" s="23" t="n"/>
+      <c r="AA40" s="23" t="n"/>
+      <c r="AB40" s="23" t="n"/>
+      <c r="AC40" s="23" t="n"/>
+      <c r="AD40" s="23" t="n"/>
+      <c r="AE40" s="23" t="n"/>
+      <c r="AF40" s="23" t="n"/>
+      <c r="AG40" s="23" t="n"/>
+      <c r="AH40" s="23" t="n"/>
+      <c r="AI40" s="23" t="n"/>
+      <c r="AJ40" s="23" t="n"/>
+      <c r="AK40" s="23" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="25" t="n"/>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="25" t="n"/>
-      <c r="D41" s="25" t="n"/>
-      <c r="E41" s="25" t="n"/>
-      <c r="F41" s="25" t="n"/>
-      <c r="G41" s="25" t="n"/>
-      <c r="H41" s="25" t="n"/>
-      <c r="I41" s="25" t="n"/>
-      <c r="J41" s="25" t="inlineStr">
-        <is>
-          <t>REFERENCE DEDUCTION</t>
-        </is>
-      </c>
-      <c r="K41" s="25" t="n"/>
-      <c r="L41" s="25" t="n"/>
-      <c r="M41" s="25" t="n"/>
-      <c r="N41" s="25" t="n"/>
-      <c r="O41" s="25" t="n"/>
-      <c r="P41" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="25" t="n"/>
-      <c r="R41" s="25" t="n"/>
-      <c r="S41" s="25" t="n"/>
-      <c r="T41" s="25" t="n"/>
-      <c r="U41" s="25" t="n"/>
-      <c r="V41" s="25" t="n"/>
-      <c r="W41" s="25" t="n"/>
-      <c r="X41" s="25" t="n"/>
-      <c r="Y41" s="25" t="n"/>
-      <c r="Z41" s="25" t="n"/>
-      <c r="AA41" s="25" t="n"/>
-      <c r="AB41" s="25" t="n"/>
-      <c r="AC41" s="25" t="n"/>
-      <c r="AD41" s="25" t="n"/>
-      <c r="AE41" s="25" t="n"/>
-      <c r="AF41" s="25" t="n"/>
-      <c r="AG41" s="25" t="n"/>
-      <c r="AH41" s="25" t="n"/>
-      <c r="AI41" s="25" t="n"/>
-      <c r="AJ41" s="25" t="n"/>
-      <c r="AK41" s="25" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="25" t="n"/>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="25" t="n"/>
-      <c r="D42" s="25" t="n"/>
-      <c r="E42" s="25" t="n"/>
-      <c r="F42" s="25" t="n"/>
-      <c r="G42" s="25" t="n"/>
-      <c r="H42" s="25" t="n"/>
-      <c r="I42" s="25" t="n"/>
-      <c r="J42" s="25" t="inlineStr">
-        <is>
-          <t>REFERENCE ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="K42" s="25" t="n"/>
-      <c r="L42" s="25" t="n"/>
-      <c r="M42" s="25" t="n"/>
-      <c r="N42" s="25" t="n"/>
-      <c r="O42" s="25" t="n"/>
-      <c r="P42" s="26">
-        <f>P38+P39+P40-P41</f>
-        <v/>
-      </c>
-      <c r="Q42" s="25" t="n"/>
-      <c r="R42" s="25" t="n"/>
-      <c r="S42" s="25" t="n"/>
-      <c r="T42" s="25" t="n"/>
-      <c r="U42" s="25" t="n"/>
-      <c r="V42" s="25" t="n"/>
-      <c r="W42" s="25" t="n"/>
-      <c r="X42" s="25" t="n"/>
-      <c r="Y42" s="25" t="n"/>
-      <c r="Z42" s="25" t="n"/>
-      <c r="AA42" s="25" t="n"/>
-      <c r="AB42" s="25" t="n"/>
-      <c r="AC42" s="25" t="n"/>
-      <c r="AD42" s="25" t="n"/>
-      <c r="AE42" s="25" t="n"/>
-      <c r="AF42" s="25" t="n"/>
-      <c r="AG42" s="25" t="n"/>
-      <c r="AH42" s="25" t="n"/>
-      <c r="AI42" s="25" t="n"/>
-      <c r="AJ42" s="25" t="n"/>
-      <c r="AK42" s="25" t="n"/>
+      <c r="A41" s="23" t="n"/>
+      <c r="B41" s="23" t="n"/>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="23" t="n"/>
+      <c r="H41" s="23" t="n"/>
+      <c r="I41" s="23" t="n"/>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>REFERENCE NET TOTAL</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="n"/>
+      <c r="L41" s="23" t="n"/>
+      <c r="M41" s="23" t="n"/>
+      <c r="N41" s="23" t="n"/>
+      <c r="O41" s="23" t="n"/>
+      <c r="P41" s="24">
+        <f>P35+P40</f>
+        <v/>
+      </c>
+      <c r="Q41" s="23" t="n"/>
+      <c r="R41" s="23" t="n"/>
+      <c r="S41" s="23" t="n"/>
+      <c r="T41" s="23" t="n"/>
+      <c r="U41" s="23" t="n"/>
+      <c r="V41" s="23" t="n"/>
+      <c r="W41" s="23" t="n"/>
+      <c r="X41" s="23" t="n"/>
+      <c r="Y41" s="23" t="n"/>
+      <c r="Z41" s="23" t="n"/>
+      <c r="AA41" s="23" t="n"/>
+      <c r="AB41" s="23" t="n"/>
+      <c r="AC41" s="23" t="n"/>
+      <c r="AD41" s="23" t="n"/>
+      <c r="AE41" s="23" t="n"/>
+      <c r="AF41" s="23" t="n"/>
+      <c r="AG41" s="23" t="n"/>
+      <c r="AH41" s="23" t="n"/>
+      <c r="AI41" s="23" t="n"/>
+      <c r="AJ41" s="23" t="n"/>
+      <c r="AK41" s="23" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="25" t="n"/>
-      <c r="B43" s="25" t="n"/>
-      <c r="C43" s="25" t="n"/>
-      <c r="D43" s="25" t="n"/>
-      <c r="E43" s="25" t="n"/>
-      <c r="F43" s="25" t="n"/>
-      <c r="G43" s="25" t="n"/>
-      <c r="H43" s="25" t="n"/>
-      <c r="I43" s="25" t="n"/>
-      <c r="J43" s="25" t="inlineStr">
-        <is>
-          <t>REFERENCE NET TOTAL</t>
-        </is>
-      </c>
-      <c r="K43" s="25" t="n"/>
-      <c r="L43" s="25" t="n"/>
-      <c r="M43" s="25" t="n"/>
-      <c r="N43" s="25" t="n"/>
-      <c r="O43" s="25" t="n"/>
-      <c r="P43" s="26">
-        <f>P37+P42</f>
-        <v/>
-      </c>
-      <c r="Q43" s="25" t="n"/>
-      <c r="R43" s="25" t="n"/>
-      <c r="S43" s="25" t="n"/>
-      <c r="T43" s="25" t="n"/>
-      <c r="U43" s="25" t="n"/>
-      <c r="V43" s="25" t="n"/>
-      <c r="W43" s="25" t="n"/>
-      <c r="X43" s="25" t="n"/>
-      <c r="Y43" s="25" t="n"/>
-      <c r="Z43" s="25" t="n"/>
-      <c r="AA43" s="25" t="n"/>
-      <c r="AB43" s="25" t="n"/>
-      <c r="AC43" s="25" t="n"/>
-      <c r="AD43" s="25" t="n"/>
-      <c r="AE43" s="25" t="n"/>
-      <c r="AF43" s="25" t="n"/>
-      <c r="AG43" s="25" t="n"/>
-      <c r="AH43" s="25" t="n"/>
-      <c r="AI43" s="25" t="n"/>
-      <c r="AJ43" s="25" t="n"/>
-      <c r="AK43" s="25" t="n"/>
+      <c r="A43" s="23" t="n"/>
+      <c r="B43" s="23" t="n"/>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="23" t="n"/>
+      <c r="F43" s="23" t="n"/>
+      <c r="G43" s="23" t="n"/>
+      <c r="H43" s="23" t="n"/>
+      <c r="I43" s="23" t="n"/>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>COMBINED ITEMS TOTAL</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="n"/>
+      <c r="L43" s="23" t="n"/>
+      <c r="M43" s="23" t="n"/>
+      <c r="N43" s="23" t="n"/>
+      <c r="O43" s="23" t="n"/>
+      <c r="P43" s="24">
+        <f>P6+P35</f>
+        <v/>
+      </c>
+      <c r="Q43" s="23" t="n"/>
+      <c r="R43" s="23" t="n"/>
+      <c r="S43" s="23" t="n"/>
+      <c r="T43" s="23" t="n"/>
+      <c r="U43" s="23" t="n"/>
+      <c r="V43" s="23" t="n"/>
+      <c r="W43" s="23" t="n"/>
+      <c r="X43" s="23" t="n"/>
+      <c r="Y43" s="23" t="n"/>
+      <c r="Z43" s="23" t="n"/>
+      <c r="AA43" s="23" t="n"/>
+      <c r="AB43" s="23" t="n"/>
+      <c r="AC43" s="23" t="n"/>
+      <c r="AD43" s="23" t="n"/>
+      <c r="AE43" s="23" t="n"/>
+      <c r="AF43" s="23" t="n"/>
+      <c r="AG43" s="23" t="n"/>
+      <c r="AH43" s="23" t="n"/>
+      <c r="AI43" s="23" t="n"/>
+      <c r="AJ43" s="23" t="n"/>
+      <c r="AK43" s="23" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="n"/>
+      <c r="B44" s="23" t="n"/>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="23" t="n"/>
+      <c r="E44" s="23" t="n"/>
+      <c r="F44" s="23" t="n"/>
+      <c r="G44" s="23" t="n"/>
+      <c r="H44" s="23" t="n"/>
+      <c r="I44" s="23" t="n"/>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>FULL INVOICE FREIGHT</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="n"/>
+      <c r="L44" s="23" t="n"/>
+      <c r="M44" s="23" t="n"/>
+      <c r="N44" s="23" t="n"/>
+      <c r="O44" s="23" t="n"/>
+      <c r="P44" s="24">
+        <f>P10+P36</f>
+        <v/>
+      </c>
+      <c r="Q44" s="23" t="n"/>
+      <c r="R44" s="23" t="n"/>
+      <c r="S44" s="23" t="n"/>
+      <c r="T44" s="23" t="n"/>
+      <c r="U44" s="23" t="n"/>
+      <c r="V44" s="23" t="n"/>
+      <c r="W44" s="23" t="n"/>
+      <c r="X44" s="23" t="n"/>
+      <c r="Y44" s="23" t="n"/>
+      <c r="Z44" s="23" t="n"/>
+      <c r="AA44" s="23" t="n"/>
+      <c r="AB44" s="23" t="n"/>
+      <c r="AC44" s="23" t="n"/>
+      <c r="AD44" s="23" t="n"/>
+      <c r="AE44" s="23" t="n"/>
+      <c r="AF44" s="23" t="n"/>
+      <c r="AG44" s="23" t="n"/>
+      <c r="AH44" s="23" t="n"/>
+      <c r="AI44" s="23" t="n"/>
+      <c r="AJ44" s="23" t="n"/>
+      <c r="AK44" s="23" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="25" t="n"/>
-      <c r="B45" s="25" t="n"/>
-      <c r="C45" s="25" t="n"/>
-      <c r="D45" s="25" t="n"/>
-      <c r="E45" s="25" t="n"/>
-      <c r="F45" s="25" t="n"/>
-      <c r="G45" s="25" t="n"/>
-      <c r="H45" s="25" t="n"/>
-      <c r="I45" s="25" t="n"/>
-      <c r="J45" s="25" t="inlineStr">
-        <is>
-          <t>COMBINED ITEMS TOTAL</t>
-        </is>
-      </c>
-      <c r="K45" s="25" t="n"/>
-      <c r="L45" s="25" t="n"/>
-      <c r="M45" s="25" t="n"/>
-      <c r="N45" s="25" t="n"/>
-      <c r="O45" s="25" t="n"/>
-      <c r="P45" s="26">
-        <f>P6+P37</f>
-        <v/>
-      </c>
-      <c r="Q45" s="25" t="n"/>
-      <c r="R45" s="25" t="n"/>
-      <c r="S45" s="25" t="n"/>
-      <c r="T45" s="25" t="n"/>
-      <c r="U45" s="25" t="n"/>
-      <c r="V45" s="25" t="n"/>
-      <c r="W45" s="25" t="n"/>
-      <c r="X45" s="25" t="n"/>
-      <c r="Y45" s="25" t="n"/>
-      <c r="Z45" s="25" t="n"/>
-      <c r="AA45" s="25" t="n"/>
-      <c r="AB45" s="25" t="n"/>
-      <c r="AC45" s="25" t="n"/>
-      <c r="AD45" s="25" t="n"/>
-      <c r="AE45" s="25" t="n"/>
-      <c r="AF45" s="25" t="n"/>
-      <c r="AG45" s="25" t="n"/>
-      <c r="AH45" s="25" t="n"/>
-      <c r="AI45" s="25" t="n"/>
-      <c r="AJ45" s="25" t="n"/>
-      <c r="AK45" s="25" t="n"/>
+      <c r="A45" s="23" t="n"/>
+      <c r="B45" s="23" t="n"/>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="23" t="n"/>
+      <c r="G45" s="23" t="n"/>
+      <c r="H45" s="23" t="n"/>
+      <c r="I45" s="23" t="n"/>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>FULL INVOICE INSURANCE</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="n"/>
+      <c r="L45" s="23" t="n"/>
+      <c r="M45" s="23" t="n"/>
+      <c r="N45" s="23" t="n"/>
+      <c r="O45" s="23" t="n"/>
+      <c r="P45" s="24">
+        <f>P11+P37</f>
+        <v/>
+      </c>
+      <c r="Q45" s="23" t="n"/>
+      <c r="R45" s="23" t="n"/>
+      <c r="S45" s="23" t="n"/>
+      <c r="T45" s="23" t="n"/>
+      <c r="U45" s="23" t="n"/>
+      <c r="V45" s="23" t="n"/>
+      <c r="W45" s="23" t="n"/>
+      <c r="X45" s="23" t="n"/>
+      <c r="Y45" s="23" t="n"/>
+      <c r="Z45" s="23" t="n"/>
+      <c r="AA45" s="23" t="n"/>
+      <c r="AB45" s="23" t="n"/>
+      <c r="AC45" s="23" t="n"/>
+      <c r="AD45" s="23" t="n"/>
+      <c r="AE45" s="23" t="n"/>
+      <c r="AF45" s="23" t="n"/>
+      <c r="AG45" s="23" t="n"/>
+      <c r="AH45" s="23" t="n"/>
+      <c r="AI45" s="23" t="n"/>
+      <c r="AJ45" s="23" t="n"/>
+      <c r="AK45" s="23" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="25" t="n"/>
-      <c r="B46" s="25" t="n"/>
-      <c r="C46" s="25" t="n"/>
-      <c r="D46" s="25" t="n"/>
-      <c r="E46" s="25" t="n"/>
-      <c r="F46" s="25" t="n"/>
-      <c r="G46" s="25" t="n"/>
-      <c r="H46" s="25" t="n"/>
-      <c r="I46" s="25" t="n"/>
-      <c r="J46" s="25" t="inlineStr">
-        <is>
-          <t>FULL INVOICE FREIGHT</t>
-        </is>
-      </c>
-      <c r="K46" s="25" t="n"/>
-      <c r="L46" s="25" t="n"/>
-      <c r="M46" s="25" t="n"/>
-      <c r="N46" s="25" t="n"/>
-      <c r="O46" s="25" t="n"/>
-      <c r="P46" s="26">
-        <f>P10+P38</f>
-        <v/>
-      </c>
-      <c r="Q46" s="25" t="n"/>
-      <c r="R46" s="25" t="n"/>
-      <c r="S46" s="25" t="n"/>
-      <c r="T46" s="25" t="n"/>
-      <c r="U46" s="25" t="n"/>
-      <c r="V46" s="25" t="n"/>
-      <c r="W46" s="25" t="n"/>
-      <c r="X46" s="25" t="n"/>
-      <c r="Y46" s="25" t="n"/>
-      <c r="Z46" s="25" t="n"/>
-      <c r="AA46" s="25" t="n"/>
-      <c r="AB46" s="25" t="n"/>
-      <c r="AC46" s="25" t="n"/>
-      <c r="AD46" s="25" t="n"/>
-      <c r="AE46" s="25" t="n"/>
-      <c r="AF46" s="25" t="n"/>
-      <c r="AG46" s="25" t="n"/>
-      <c r="AH46" s="25" t="n"/>
-      <c r="AI46" s="25" t="n"/>
-      <c r="AJ46" s="25" t="n"/>
-      <c r="AK46" s="25" t="n"/>
+      <c r="A46" s="23" t="n"/>
+      <c r="B46" s="23" t="n"/>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="23" t="n"/>
+      <c r="E46" s="23" t="n"/>
+      <c r="F46" s="23" t="n"/>
+      <c r="G46" s="23" t="n"/>
+      <c r="H46" s="23" t="n"/>
+      <c r="I46" s="23" t="n"/>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>FULL INVOICE OTHER COST</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="n"/>
+      <c r="L46" s="23" t="n"/>
+      <c r="M46" s="23" t="n"/>
+      <c r="N46" s="23" t="n"/>
+      <c r="O46" s="23" t="n"/>
+      <c r="P46" s="24">
+        <f>P12+P38</f>
+        <v/>
+      </c>
+      <c r="Q46" s="23" t="n"/>
+      <c r="R46" s="23" t="n"/>
+      <c r="S46" s="23" t="n"/>
+      <c r="T46" s="23" t="n"/>
+      <c r="U46" s="23" t="n"/>
+      <c r="V46" s="23" t="n"/>
+      <c r="W46" s="23" t="n"/>
+      <c r="X46" s="23" t="n"/>
+      <c r="Y46" s="23" t="n"/>
+      <c r="Z46" s="23" t="n"/>
+      <c r="AA46" s="23" t="n"/>
+      <c r="AB46" s="23" t="n"/>
+      <c r="AC46" s="23" t="n"/>
+      <c r="AD46" s="23" t="n"/>
+      <c r="AE46" s="23" t="n"/>
+      <c r="AF46" s="23" t="n"/>
+      <c r="AG46" s="23" t="n"/>
+      <c r="AH46" s="23" t="n"/>
+      <c r="AI46" s="23" t="n"/>
+      <c r="AJ46" s="23" t="n"/>
+      <c r="AK46" s="23" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="25" t="n"/>
-      <c r="B47" s="25" t="n"/>
-      <c r="C47" s="25" t="n"/>
-      <c r="D47" s="25" t="n"/>
-      <c r="E47" s="25" t="n"/>
-      <c r="F47" s="25" t="n"/>
-      <c r="G47" s="25" t="n"/>
-      <c r="H47" s="25" t="n"/>
-      <c r="I47" s="25" t="n"/>
-      <c r="J47" s="25" t="inlineStr">
-        <is>
-          <t>FULL INVOICE INSURANCE</t>
-        </is>
-      </c>
-      <c r="K47" s="25" t="n"/>
-      <c r="L47" s="25" t="n"/>
-      <c r="M47" s="25" t="n"/>
-      <c r="N47" s="25" t="n"/>
-      <c r="O47" s="25" t="n"/>
-      <c r="P47" s="26">
-        <f>P11+P39</f>
-        <v/>
-      </c>
-      <c r="Q47" s="25" t="n"/>
-      <c r="R47" s="25" t="n"/>
-      <c r="S47" s="25" t="n"/>
-      <c r="T47" s="25" t="n"/>
-      <c r="U47" s="25" t="n"/>
-      <c r="V47" s="25" t="n"/>
-      <c r="W47" s="25" t="n"/>
-      <c r="X47" s="25" t="n"/>
-      <c r="Y47" s="25" t="n"/>
-      <c r="Z47" s="25" t="n"/>
-      <c r="AA47" s="25" t="n"/>
-      <c r="AB47" s="25" t="n"/>
-      <c r="AC47" s="25" t="n"/>
-      <c r="AD47" s="25" t="n"/>
-      <c r="AE47" s="25" t="n"/>
-      <c r="AF47" s="25" t="n"/>
-      <c r="AG47" s="25" t="n"/>
-      <c r="AH47" s="25" t="n"/>
-      <c r="AI47" s="25" t="n"/>
-      <c r="AJ47" s="25" t="n"/>
-      <c r="AK47" s="25" t="n"/>
+      <c r="A47" s="23" t="n"/>
+      <c r="B47" s="23" t="n"/>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="23" t="n"/>
+      <c r="E47" s="23" t="n"/>
+      <c r="F47" s="23" t="n"/>
+      <c r="G47" s="23" t="n"/>
+      <c r="H47" s="23" t="n"/>
+      <c r="I47" s="23" t="n"/>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>FULL INVOICE DEDUCTION</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="n"/>
+      <c r="L47" s="23" t="n"/>
+      <c r="M47" s="23" t="n"/>
+      <c r="N47" s="23" t="n"/>
+      <c r="O47" s="23" t="n"/>
+      <c r="P47" s="24">
+        <f>P13+P39</f>
+        <v/>
+      </c>
+      <c r="Q47" s="23" t="n"/>
+      <c r="R47" s="23" t="n"/>
+      <c r="S47" s="23" t="n"/>
+      <c r="T47" s="23" t="n"/>
+      <c r="U47" s="23" t="n"/>
+      <c r="V47" s="23" t="n"/>
+      <c r="W47" s="23" t="n"/>
+      <c r="X47" s="23" t="n"/>
+      <c r="Y47" s="23" t="n"/>
+      <c r="Z47" s="23" t="n"/>
+      <c r="AA47" s="23" t="n"/>
+      <c r="AB47" s="23" t="n"/>
+      <c r="AC47" s="23" t="n"/>
+      <c r="AD47" s="23" t="n"/>
+      <c r="AE47" s="23" t="n"/>
+      <c r="AF47" s="23" t="n"/>
+      <c r="AG47" s="23" t="n"/>
+      <c r="AH47" s="23" t="n"/>
+      <c r="AI47" s="23" t="n"/>
+      <c r="AJ47" s="23" t="n"/>
+      <c r="AK47" s="23" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="25" t="n"/>
-      <c r="B48" s="25" t="n"/>
-      <c r="C48" s="25" t="n"/>
-      <c r="D48" s="25" t="n"/>
-      <c r="E48" s="25" t="n"/>
-      <c r="F48" s="25" t="n"/>
-      <c r="G48" s="25" t="n"/>
-      <c r="H48" s="25" t="n"/>
-      <c r="I48" s="25" t="n"/>
-      <c r="J48" s="25" t="inlineStr">
-        <is>
-          <t>FULL INVOICE OTHER COST</t>
-        </is>
-      </c>
-      <c r="K48" s="25" t="n"/>
-      <c r="L48" s="25" t="n"/>
-      <c r="M48" s="25" t="n"/>
-      <c r="N48" s="25" t="n"/>
-      <c r="O48" s="25" t="n"/>
-      <c r="P48" s="26">
-        <f>P12+P40</f>
-        <v/>
-      </c>
-      <c r="Q48" s="25" t="n"/>
-      <c r="R48" s="25" t="n"/>
-      <c r="S48" s="25" t="n"/>
-      <c r="T48" s="25" t="n"/>
-      <c r="U48" s="25" t="n"/>
-      <c r="V48" s="25" t="n"/>
-      <c r="W48" s="25" t="n"/>
-      <c r="X48" s="25" t="n"/>
-      <c r="Y48" s="25" t="n"/>
-      <c r="Z48" s="25" t="n"/>
-      <c r="AA48" s="25" t="n"/>
-      <c r="AB48" s="25" t="n"/>
-      <c r="AC48" s="25" t="n"/>
-      <c r="AD48" s="25" t="n"/>
-      <c r="AE48" s="25" t="n"/>
-      <c r="AF48" s="25" t="n"/>
-      <c r="AG48" s="25" t="n"/>
-      <c r="AH48" s="25" t="n"/>
-      <c r="AI48" s="25" t="n"/>
-      <c r="AJ48" s="25" t="n"/>
-      <c r="AK48" s="25" t="n"/>
+      <c r="A48" s="23" t="n"/>
+      <c r="B48" s="23" t="n"/>
+      <c r="C48" s="23" t="n"/>
+      <c r="D48" s="23" t="n"/>
+      <c r="E48" s="23" t="n"/>
+      <c r="F48" s="23" t="n"/>
+      <c r="G48" s="23" t="n"/>
+      <c r="H48" s="23" t="n"/>
+      <c r="I48" s="23" t="n"/>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>FULL ADJUSTMENTS</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="n"/>
+      <c r="L48" s="23" t="n"/>
+      <c r="M48" s="23" t="n"/>
+      <c r="N48" s="23" t="n"/>
+      <c r="O48" s="23" t="n"/>
+      <c r="P48" s="24">
+        <f>P44+P45+P46-P47</f>
+        <v/>
+      </c>
+      <c r="Q48" s="23" t="n"/>
+      <c r="R48" s="23" t="n"/>
+      <c r="S48" s="23" t="n"/>
+      <c r="T48" s="23" t="n"/>
+      <c r="U48" s="23" t="n"/>
+      <c r="V48" s="23" t="n"/>
+      <c r="W48" s="23" t="n"/>
+      <c r="X48" s="23" t="n"/>
+      <c r="Y48" s="23" t="n"/>
+      <c r="Z48" s="23" t="n"/>
+      <c r="AA48" s="23" t="n"/>
+      <c r="AB48" s="23" t="n"/>
+      <c r="AC48" s="23" t="n"/>
+      <c r="AD48" s="23" t="n"/>
+      <c r="AE48" s="23" t="n"/>
+      <c r="AF48" s="23" t="n"/>
+      <c r="AG48" s="23" t="n"/>
+      <c r="AH48" s="23" t="n"/>
+      <c r="AI48" s="23" t="n"/>
+      <c r="AJ48" s="23" t="n"/>
+      <c r="AK48" s="23" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="25" t="n"/>
-      <c r="B49" s="25" t="n"/>
-      <c r="C49" s="25" t="n"/>
-      <c r="D49" s="25" t="n"/>
-      <c r="E49" s="25" t="n"/>
-      <c r="F49" s="25" t="n"/>
-      <c r="G49" s="25" t="n"/>
-      <c r="H49" s="25" t="n"/>
-      <c r="I49" s="25" t="n"/>
-      <c r="J49" s="25" t="inlineStr">
-        <is>
-          <t>FULL INVOICE DEDUCTION</t>
-        </is>
-      </c>
-      <c r="K49" s="25" t="n"/>
-      <c r="L49" s="25" t="n"/>
-      <c r="M49" s="25" t="n"/>
-      <c r="N49" s="25" t="n"/>
-      <c r="O49" s="25" t="n"/>
-      <c r="P49" s="26">
-        <f>P13+P41</f>
-        <v/>
-      </c>
-      <c r="Q49" s="25" t="n"/>
-      <c r="R49" s="25" t="n"/>
-      <c r="S49" s="25" t="n"/>
-      <c r="T49" s="25" t="n"/>
-      <c r="U49" s="25" t="n"/>
-      <c r="V49" s="25" t="n"/>
-      <c r="W49" s="25" t="n"/>
-      <c r="X49" s="25" t="n"/>
-      <c r="Y49" s="25" t="n"/>
-      <c r="Z49" s="25" t="n"/>
-      <c r="AA49" s="25" t="n"/>
-      <c r="AB49" s="25" t="n"/>
-      <c r="AC49" s="25" t="n"/>
-      <c r="AD49" s="25" t="n"/>
-      <c r="AE49" s="25" t="n"/>
-      <c r="AF49" s="25" t="n"/>
-      <c r="AG49" s="25" t="n"/>
-      <c r="AH49" s="25" t="n"/>
-      <c r="AI49" s="25" t="n"/>
-      <c r="AJ49" s="25" t="n"/>
-      <c r="AK49" s="25" t="n"/>
+      <c r="A49" s="23" t="n"/>
+      <c r="B49" s="23" t="n"/>
+      <c r="C49" s="23" t="n"/>
+      <c r="D49" s="23" t="n"/>
+      <c r="E49" s="23" t="n"/>
+      <c r="F49" s="23" t="n"/>
+      <c r="G49" s="23" t="n"/>
+      <c r="H49" s="23" t="n"/>
+      <c r="I49" s="23" t="n"/>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>COMBINED NET TOTAL</t>
+        </is>
+      </c>
+      <c r="K49" s="23" t="n"/>
+      <c r="L49" s="23" t="n"/>
+      <c r="M49" s="23" t="n"/>
+      <c r="N49" s="23" t="n"/>
+      <c r="O49" s="23" t="n"/>
+      <c r="P49" s="24">
+        <f>P43+P48</f>
+        <v/>
+      </c>
+      <c r="Q49" s="23" t="n"/>
+      <c r="R49" s="23" t="n"/>
+      <c r="S49" s="23" t="n"/>
+      <c r="T49" s="23" t="n"/>
+      <c r="U49" s="23" t="n"/>
+      <c r="V49" s="23" t="n"/>
+      <c r="W49" s="23" t="n"/>
+      <c r="X49" s="23" t="n"/>
+      <c r="Y49" s="23" t="n"/>
+      <c r="Z49" s="23" t="n"/>
+      <c r="AA49" s="23" t="n"/>
+      <c r="AB49" s="23" t="n"/>
+      <c r="AC49" s="23" t="n"/>
+      <c r="AD49" s="23" t="n"/>
+      <c r="AE49" s="23" t="n"/>
+      <c r="AF49" s="23" t="n"/>
+      <c r="AG49" s="23" t="n"/>
+      <c r="AH49" s="23" t="n"/>
+      <c r="AI49" s="23" t="n"/>
+      <c r="AJ49" s="23" t="n"/>
+      <c r="AK49" s="23" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="25" t="n"/>
-      <c r="B50" s="25" t="n"/>
-      <c r="C50" s="25" t="n"/>
-      <c r="D50" s="25" t="n"/>
-      <c r="E50" s="25" t="n"/>
-      <c r="F50" s="25" t="n"/>
-      <c r="G50" s="25" t="n"/>
-      <c r="H50" s="25" t="n"/>
-      <c r="I50" s="25" t="n"/>
-      <c r="J50" s="25" t="inlineStr">
-        <is>
-          <t>FULL ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="K50" s="25" t="n"/>
-      <c r="L50" s="25" t="n"/>
-      <c r="M50" s="25" t="n"/>
-      <c r="N50" s="25" t="n"/>
-      <c r="O50" s="25" t="n"/>
-      <c r="P50" s="26">
-        <f>P46+P47+P48-P49</f>
-        <v/>
-      </c>
-      <c r="Q50" s="25" t="n"/>
-      <c r="R50" s="25" t="n"/>
-      <c r="S50" s="25" t="n"/>
-      <c r="T50" s="25" t="n"/>
-      <c r="U50" s="25" t="n"/>
-      <c r="V50" s="25" t="n"/>
-      <c r="W50" s="25" t="n"/>
-      <c r="X50" s="25" t="n"/>
-      <c r="Y50" s="25" t="n"/>
-      <c r="Z50" s="25" t="n"/>
-      <c r="AA50" s="25" t="n"/>
-      <c r="AB50" s="25" t="n"/>
-      <c r="AC50" s="25" t="n"/>
-      <c r="AD50" s="25" t="n"/>
-      <c r="AE50" s="25" t="n"/>
-      <c r="AF50" s="25" t="n"/>
-      <c r="AG50" s="25" t="n"/>
-      <c r="AH50" s="25" t="n"/>
-      <c r="AI50" s="25" t="n"/>
-      <c r="AJ50" s="25" t="n"/>
-      <c r="AK50" s="25" t="n"/>
+      <c r="A50" s="23" t="n"/>
+      <c r="B50" s="23" t="n"/>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="23" t="n"/>
+      <c r="E50" s="23" t="n"/>
+      <c r="F50" s="23" t="n"/>
+      <c r="G50" s="23" t="n"/>
+      <c r="H50" s="23" t="n"/>
+      <c r="I50" s="23" t="n"/>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>FULL INVOICE TOTAL</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="n"/>
+      <c r="L50" s="23" t="n"/>
+      <c r="M50" s="23" t="n"/>
+      <c r="N50" s="23" t="n"/>
+      <c r="O50" s="23" t="n"/>
+      <c r="P50" s="24" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="Q50" s="23" t="n"/>
+      <c r="R50" s="23" t="n"/>
+      <c r="S50" s="23" t="n"/>
+      <c r="T50" s="23" t="n"/>
+      <c r="U50" s="23" t="n"/>
+      <c r="V50" s="23" t="n"/>
+      <c r="W50" s="23" t="n"/>
+      <c r="X50" s="23" t="n"/>
+      <c r="Y50" s="23" t="n"/>
+      <c r="Z50" s="23" t="n"/>
+      <c r="AA50" s="23" t="n"/>
+      <c r="AB50" s="23" t="n"/>
+      <c r="AC50" s="23" t="n"/>
+      <c r="AD50" s="23" t="n"/>
+      <c r="AE50" s="23" t="n"/>
+      <c r="AF50" s="23" t="n"/>
+      <c r="AG50" s="23" t="n"/>
+      <c r="AH50" s="23" t="n"/>
+      <c r="AI50" s="23" t="n"/>
+      <c r="AJ50" s="23" t="n"/>
+      <c r="AK50" s="23" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="25" t="n"/>
-      <c r="B51" s="25" t="n"/>
-      <c r="C51" s="25" t="n"/>
-      <c r="D51" s="25" t="n"/>
-      <c r="E51" s="25" t="n"/>
-      <c r="F51" s="25" t="n"/>
-      <c r="G51" s="25" t="n"/>
-      <c r="H51" s="25" t="n"/>
-      <c r="I51" s="25" t="n"/>
-      <c r="J51" s="25" t="inlineStr">
-        <is>
-          <t>COMBINED NET TOTAL</t>
-        </is>
-      </c>
-      <c r="K51" s="25" t="n"/>
-      <c r="L51" s="25" t="n"/>
-      <c r="M51" s="25" t="n"/>
-      <c r="N51" s="25" t="n"/>
-      <c r="O51" s="25" t="n"/>
-      <c r="P51" s="26">
-        <f>P45+P50</f>
-        <v/>
-      </c>
-      <c r="Q51" s="25" t="n"/>
-      <c r="R51" s="25" t="n"/>
-      <c r="S51" s="25" t="n"/>
-      <c r="T51" s="25" t="n"/>
-      <c r="U51" s="25" t="n"/>
-      <c r="V51" s="25" t="n"/>
-      <c r="W51" s="25" t="n"/>
-      <c r="X51" s="25" t="n"/>
-      <c r="Y51" s="25" t="n"/>
-      <c r="Z51" s="25" t="n"/>
-      <c r="AA51" s="25" t="n"/>
-      <c r="AB51" s="25" t="n"/>
-      <c r="AC51" s="25" t="n"/>
-      <c r="AD51" s="25" t="n"/>
-      <c r="AE51" s="25" t="n"/>
-      <c r="AF51" s="25" t="n"/>
-      <c r="AG51" s="25" t="n"/>
-      <c r="AH51" s="25" t="n"/>
-      <c r="AI51" s="25" t="n"/>
-      <c r="AJ51" s="25" t="n"/>
-      <c r="AK51" s="25" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="25" t="n"/>
-      <c r="B52" s="25" t="n"/>
-      <c r="C52" s="25" t="n"/>
-      <c r="D52" s="25" t="n"/>
-      <c r="E52" s="25" t="n"/>
-      <c r="F52" s="25" t="n"/>
-      <c r="G52" s="25" t="n"/>
-      <c r="H52" s="25" t="n"/>
-      <c r="I52" s="25" t="n"/>
-      <c r="J52" s="25" t="inlineStr">
-        <is>
-          <t>FULL INVOICE TOTAL</t>
-        </is>
-      </c>
-      <c r="K52" s="25" t="n"/>
-      <c r="L52" s="25" t="n"/>
-      <c r="M52" s="25" t="n"/>
-      <c r="N52" s="25" t="n"/>
-      <c r="O52" s="25" t="n"/>
-      <c r="P52" s="26" t="n">
-        <v>61.58</v>
-      </c>
-      <c r="Q52" s="25" t="n"/>
-      <c r="R52" s="25" t="n"/>
-      <c r="S52" s="25" t="n"/>
-      <c r="T52" s="25" t="n"/>
-      <c r="U52" s="25" t="n"/>
-      <c r="V52" s="25" t="n"/>
-      <c r="W52" s="25" t="n"/>
-      <c r="X52" s="25" t="n"/>
-      <c r="Y52" s="25" t="n"/>
-      <c r="Z52" s="25" t="n"/>
-      <c r="AA52" s="25" t="n"/>
-      <c r="AB52" s="25" t="n"/>
-      <c r="AC52" s="25" t="n"/>
-      <c r="AD52" s="25" t="n"/>
-      <c r="AE52" s="25" t="n"/>
-      <c r="AF52" s="25" t="n"/>
-      <c r="AG52" s="25" t="n"/>
-      <c r="AH52" s="25" t="n"/>
-      <c r="AI52" s="25" t="n"/>
-      <c r="AJ52" s="25" t="n"/>
-      <c r="AK52" s="25" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="25" t="n"/>
-      <c r="B53" s="25" t="n"/>
-      <c r="C53" s="25" t="n"/>
-      <c r="D53" s="25" t="n"/>
-      <c r="E53" s="25" t="n"/>
-      <c r="F53" s="25" t="n"/>
-      <c r="G53" s="25" t="n"/>
-      <c r="H53" s="25" t="n"/>
-      <c r="I53" s="25" t="n"/>
-      <c r="J53" s="25" t="inlineStr">
+      <c r="A51" s="23" t="n"/>
+      <c r="B51" s="23" t="n"/>
+      <c r="C51" s="23" t="n"/>
+      <c r="D51" s="23" t="n"/>
+      <c r="E51" s="23" t="n"/>
+      <c r="F51" s="23" t="n"/>
+      <c r="G51" s="23" t="n"/>
+      <c r="H51" s="23" t="n"/>
+      <c r="I51" s="23" t="n"/>
+      <c r="J51" s="23" t="inlineStr">
         <is>
           <t>COMBINED VARIANCE CHECK</t>
         </is>
       </c>
-      <c r="K53" s="25" t="n"/>
-      <c r="L53" s="25" t="n"/>
-      <c r="M53" s="25" t="n"/>
-      <c r="N53" s="25" t="n"/>
-      <c r="O53" s="25" t="n"/>
-      <c r="P53" s="26">
-        <f>P52-P51</f>
-        <v/>
-      </c>
-      <c r="Q53" s="25" t="n"/>
-      <c r="R53" s="25" t="n"/>
-      <c r="S53" s="25" t="n"/>
-      <c r="T53" s="25" t="n"/>
-      <c r="U53" s="25" t="n"/>
-      <c r="V53" s="25" t="n"/>
-      <c r="W53" s="25" t="n"/>
-      <c r="X53" s="25" t="n"/>
-      <c r="Y53" s="25" t="n"/>
-      <c r="Z53" s="25" t="n"/>
-      <c r="AA53" s="25" t="n"/>
-      <c r="AB53" s="25" t="n"/>
-      <c r="AC53" s="25" t="n"/>
-      <c r="AD53" s="25" t="n"/>
-      <c r="AE53" s="25" t="n"/>
-      <c r="AF53" s="25" t="n"/>
-      <c r="AG53" s="25" t="n"/>
-      <c r="AH53" s="25" t="n"/>
-      <c r="AI53" s="25" t="n"/>
-      <c r="AJ53" s="25" t="n"/>
-      <c r="AK53" s="25" t="n"/>
+      <c r="K51" s="23" t="n"/>
+      <c r="L51" s="23" t="n"/>
+      <c r="M51" s="23" t="n"/>
+      <c r="N51" s="23" t="n"/>
+      <c r="O51" s="23" t="n"/>
+      <c r="P51" s="24">
+        <f>P50-P49</f>
+        <v/>
+      </c>
+      <c r="Q51" s="23" t="n"/>
+      <c r="R51" s="23" t="n"/>
+      <c r="S51" s="23" t="n"/>
+      <c r="T51" s="23" t="n"/>
+      <c r="U51" s="23" t="n"/>
+      <c r="V51" s="23" t="n"/>
+      <c r="W51" s="23" t="n"/>
+      <c r="X51" s="23" t="n"/>
+      <c r="Y51" s="23" t="n"/>
+      <c r="Z51" s="23" t="n"/>
+      <c r="AA51" s="23" t="n"/>
+      <c r="AB51" s="23" t="n"/>
+      <c r="AC51" s="23" t="n"/>
+      <c r="AD51" s="23" t="n"/>
+      <c r="AE51" s="23" t="n"/>
+      <c r="AF51" s="23" t="n"/>
+      <c r="AG51" s="23" t="n"/>
+      <c r="AH51" s="23" t="n"/>
+      <c r="AI51" s="23" t="n"/>
+      <c r="AJ51" s="23" t="n"/>
+      <c r="AK51" s="23" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
